--- a/employee_surveys/005_nap_pod_usage_interest_survey--employee_surveys.xlsx
+++ b/employee_surveys/005_nap_pod_usage_interest_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nap_pods_on_campus</t>
+          <t>nap pods on campus</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nap_pods_in_my_office</t>
+          <t>nap pods in my office</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nap_pods_in_my_home</t>
+          <t>nap pods in my home</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nap_pod</t>
+          <t>nap pod</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nap_pod</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nap_pod</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nap_pod_type_choices</t>
+          <t>nap_pod_features_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>temperature_control</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>temperature control</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>temperature_control</t>
+          <t>white_noise</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>temperature_control</t>
+          <t>white noise</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>white_noise</t>
+          <t>quiet</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>white_noise</t>
+          <t>quiet</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>quiet</t>
+          <t>nap_mat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>quiet</t>
+          <t>nap mat</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nap_pod_features_choices</t>
+          <t>nap_pod_features_frequency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nap_mat</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nap_mat</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>nap_pod_features_frequency_choices</t>
+          <t>nap_pod_favourite_frequency_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>daily</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nap_pod_favourite_frequency_choices</t>
+          <t>nap_pod_favourite_location_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>nap_pod</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>nap pod</t>
         </is>
       </c>
     </row>
@@ -1573,44 +1573,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nap_pod</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>nap_pod</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>nap_pod_favourite_location_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>nap_pod</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>nap_pod</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>nap_pod_favourite_location_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
         <is>
           <t>other</t>
         </is>
